--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий RICE_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий RICE_один эксперт.xlsx
@@ -7,7 +7,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Четкий RICE_эксперт 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итоги_четкий RICE_эксперт 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица_взаимосвязей_FR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итоги_четкий RICE_эксперт 1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +31,19 @@
       <family val="2"/>
       <sz val="8"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -61,10 +75,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -411,41 +447,47 @@
   </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.5703125" customWidth="1" min="2" max="2"/>
+    <col width="18.5703125" customWidth="1" min="3" max="3"/>
+    <col width="26.7109375" customWidth="1" min="4" max="4"/>
+    <col width="23.5703125" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>R, Reach (Охват)</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>I, Impact (Влияние)</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>С, Confidence (Уверенность)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>E, Effort (Трудозатраты)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="1" t="n">
         <v>10000</v>
       </c>
       <c r="C2" t="n">
@@ -459,12 +501,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C3" t="n">
@@ -478,12 +520,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="C4" t="n">
@@ -497,12 +539,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="1" t="n">
         <v>100</v>
       </c>
       <c r="C5" t="n">
@@ -516,12 +558,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="1" t="n">
         <v>200</v>
       </c>
       <c r="C6" t="n">
@@ -535,12 +577,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C7" t="n">
@@ -554,12 +596,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="1" t="n">
         <v>50</v>
       </c>
       <c r="C8" t="n">
@@ -573,12 +615,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="C9" t="n">
@@ -592,12 +634,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="1" t="n">
         <v>20000</v>
       </c>
       <c r="C10" t="n">
@@ -611,12 +653,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="1" t="n">
         <v>300</v>
       </c>
       <c r="C11" t="n">
@@ -640,297 +682,986 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>RICE</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Матрица взаимосвязанности функциональных требований</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" t="n">
-        <v>428.57</v>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G4" t="n">
-        <v>228.57</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>300</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FR8</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FR2</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FR5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G8" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>FR4</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>100</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FR7</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>21</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>FR6</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>13</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.77</v>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>1) Итоговый коллективный рейтинг по методу RICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Приоритизация</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Функциональное
+требование</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Reach (R)</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Impact (I)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Confidence (C)</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Effort (E)</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Итог</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>428.57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>228.57</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2) Итоговая приоритизация после учета взаимосвязанности</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Исходный рейтинг</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Скорректированный
+рейтинг</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>428.57</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>428.57</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>428.57</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>428.57</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>228.57</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>228.57</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="G2:G3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий RICE_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий RICE_один эксперт.xlsx
@@ -77,11 +77,13 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -455,219 +457,219 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>R, Reach (Охват)</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>I, Impact (Влияние)</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>С, Confidence (Уверенность)</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>E, Effort (Трудозатраты)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="1" t="n">
         <v>0.7</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="1" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="C7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="1" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="3" t="n">
         <v>20000</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="1" t="n">
         <v>0.7</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="1" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1159,7 +1161,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>1) Итоговый коллективный рейтинг по методу RICE</t>
+          <t>1) Итоговый коллективный рейтинг по методу RICE (четкая модель)</t>
         </is>
       </c>
     </row>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий RICE_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий RICE_один эксперт.xlsx
@@ -57,19 +57,13 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -89,19 +83,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1146,7 +1140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1161,414 +1155,390 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>1) Итоговый коллективный рейтинг по методу RICE (четкая модель)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+          <t>Четкий RICE - итоговая приоритизация (один эксперт)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1) Итоговый рейтинг по методу RICE (четкая модель)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Приоритизация</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Функциональное
 требование</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Reach (R)</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Impact (I)</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Confidence (C)</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Effort (E)</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Итог</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>FR1</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>FR9</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>428.57</v>
-      </c>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>FR3</t>
+          <t>FR1</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>228.57</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>FR10</t>
+          <t>FR9</t>
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>300</v>
+        <v>20000</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>140</v>
+        <v>428.57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>FR8</t>
+          <t>FR3</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
         <v>1000</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>90</v>
+        <v>228.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>FR10</t>
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>5</v>
-      </c>
       <c r="G9" s="9" t="n">
-        <v>54</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>FR5</t>
+          <t>FR8</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>FR4</t>
+          <t>FR2</t>
         </is>
       </c>
       <c r="C11" s="9" t="n">
         <v>100</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>17.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>FR7</t>
+          <t>FR5</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>3.81</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="9" t="n">
+      <c r="D15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G15" s="9" t="n">
         <v>0.77</v>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>2) Итоговая приоритизация после учета взаимосвязанности</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Место</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Исходный рейтинг</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Скорректированный
 рейтинг</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>FR1</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>600</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>FR4</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>600</v>
-      </c>
-    </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>FR9</t>
+          <t>FR1</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>428.57</v>
+        <v>600</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>428.57</v>
+        <v>600</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>FR10</t>
+          <t>FR4</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>140</v>
+        <v>17.5</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>428.57</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>FR8</t>
+          <t>FR9</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>90</v>
+        <v>428.57</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>428.57</v>
@@ -1576,93 +1546,125 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>FR3</t>
+          <t>FR10</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>228.57</v>
+        <v>140</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>228.57</v>
+        <v>428.57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>FR8</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>54</v>
+        <v>428.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>FR5</t>
+          <t>FR3</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>25</v>
+        <v>228.57</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>25</v>
+        <v>228.57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>FR7</t>
+          <t>FR2</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>3.81</v>
+        <v>54</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>3.81</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C29" s="9" t="n">
         <v>0.77</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D29" s="9" t="n">
         <v>3.81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
